--- a/01_Manual_Testing/Test_Cases.xlsx
+++ b/01_Manual_Testing/Test_Cases.xlsx
@@ -2480,12 +2480,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Should require a minimum bank size before allowing publish, with a clear message.</t>
+          <t>Should require a minimum number of questions in the bank before allowing publish, with a clear message.</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>Confirmed directly by the tester: with exactly 1 question in the bank, and only 1 of its 4 answer options filled in and marked correct (the other 3 left blank), "Save &amp; Publish" completed successfully with no minimum-size or minimum-answer-count warning at any point.</t>
+          <t>Confirmed directly by the tester: with exactly 1 question in the bank, "Save &amp; Publish" completed successfully with no minimum-question-count warning at any point. (That single question also only had 1 of its 4 answer options filled in, which the flow likewise did not flag - but the core issue being reported here is the missing minimum question count, not the answer-option count.)</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -2682,17 +2682,17 @@
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>Contradictory results across two sessions: an earlier check showed both boxes staying checked (counter read 2). A later re-check showed checking a second box automatically unchecks the first (true single-select) across 3 sequential clicks. Real production records (17BBF9B, dEMO) do show questions with 2-3 correct answers marked, so multi-select data can exist - unclear if that's only reachable via AI generation, not this interactive control.</t>
+          <t>Confirmed, no longer contradictory: only one answer can ever be selected as correct - checking a second option automatically unchecks the first, both in the admin question-authoring UI and when a crew member takes the quiz. The control is visually a checkbox but behaves as a radio button throughout. Note: a few existing production records (17BBF9B, dEMO) still show 2-3 answers marked correct from earlier/other data entry, but the live interactive control itself only ever allows one at a time - this is now settled, not an open question.</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>NEEDS RE-VERIFICATION</t>
+          <t>PASS (confirmed single-select, consistent)</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>See BUG-07. Not treated as a confirmed defect; flagged for product confirmation of intended behavior.</t>
+          <t>See BUG-07 (checkbox control visually implies multi-select but enforces single-select) - the underlying UI mismatch is still worth flagging to the dev team, but the behavior itself is confirmed and consistent, not in doubt.</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>Checking option 2 automatically unchecks option 1, and so on - true single-select behavior enforced via JS on top of checkbox inputs, not native radio semantics. Some existing production questions (17BBF9B, dEMO) already have 2-3 correct answers marked, so multi-select data can exist - unclear whether that's only reachable via AI generation and not this control (see TC-08).</t>
+          <t>Checking option 2 automatically unchecks option 1, and so on - true single-select behavior enforced via JS on top of checkbox inputs, not native radio semantics. Confirmed consistent across both the admin authoring UI and the crew-facing quiz (see TC-08) - only one answer can ever be selected. A few existing production records (17BBF9B, dEMO) still show 2-3 answers marked correct from earlier/other data entry, but the live interactive control itself never allows more than one.</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>No minimum question-bank size or answer-option count enforced before publish</t>
+          <t>No minimum number of questions enforced before publish</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -5149,25 +5149,24 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>File attached; Manual Generate chosen; exactly 1 question with only 1 of its 4 answer options filled in.</t>
+          <t>File attached; Manual Generate chosen; only 1 question added to the bank.</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>1. Build a manual bank with 1 question.
-2. Fill only 1 of its 4 answer options and mark it correct - leave the other 3 blank.
-3. Fill Training Name, Category, Duration.
-4. Click "Save &amp; Publish" and complete the "Assign assessment" modal.</t>
+          <t>1. Build a manual bank with just 1 question.
+2. Fill Training Name, Category, Duration.
+3. Click "Save &amp; Publish" and complete the "Assign assessment" modal.</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>Given the requirement is a 20-30 question bank with 5-10 assigned per crew, and each question should offer a real set of answer choices, the system should require a reasonable minimum bank size AND a minimum number of filled answer options per question before allowing publish.</t>
+          <t>Given the requirement is a 20-30 question bank with 5-10 assigned per crew, the system should require a reasonable minimum number of questions before allowing publish.</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>Confirmed by the tester: publishing succeeded with just 1 question, which itself had only 1 filled answer option (not 4) - no minimum-size or minimum-answer-count warning at any point in the flow.</t>
+          <t>Confirmed by the tester: publishing succeeded with just 1 question in the bank - no minimum-question-count warning at any point in the flow.</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
